--- a/2023-06-22_Matrix_Online-Tool_Webumsetzung.xlsx
+++ b/2023-06-22_Matrix_Online-Tool_Webumsetzung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBU_Pkw-Beschaffung_Online-Tool/Freigegebene Dokumente/General/Webumsetzung Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3A96055-E5AF-4273-AFF9-781D78CF98A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F4E389E-561E-431B-B972-85C80A9C44AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11124" tabRatio="693" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -194,6 +194,7 @@
     <author>tc={189F1E58-4F6D-4F8A-BC11-466CA5FB61C5}</author>
     <author>tc={A73FF447-0F74-4579-B0BF-65393604F85C}</author>
     <author>tc={CBB4E888-5E8C-437E-B81F-F45FE4BAF6E1}</author>
+    <author>tc={30F2D2BD-FBB0-4DD9-B48F-2ADC88252C3F}</author>
   </authors>
   <commentList>
     <comment ref="G5" authorId="0" shapeId="0" xr:uid="{56EA3F68-498D-42C7-BCF7-A65C2063460A}">
@@ -894,6 +895,16 @@
     Yeah! Susanne und ich sind happy :-)</t>
       </text>
     </comment>
+    <comment ref="G117" authorId="49" shapeId="0" xr:uid="{30F2D2BD-FBB0-4DD9-B48F-2ADC88252C3F}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Kannst du die Toolversion noch ein ganz bisschen weiter nach unten rücken? So, dass der Abstand zum unteren Seitenrand = Abstand der Logos zum oberen Fußzeilenrand
+Reply:
+    Hab ihn reduziert. Ist nicht exakt, da Text keine klare Unterkante hat</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -1407,7 +1418,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1593" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="477">
   <si>
     <t>Änderungsdatum</t>
   </si>
@@ -2003,19 +2014,25 @@
     <t>Reichweiten-Grenze für BEV von 150 auf 300 km geändert (nach Recherche mithilfe der ADAC-Datenbank durch Felix)</t>
   </si>
   <si>
+    <t>Zellen B5-8</t>
+  </si>
+  <si>
+    <t>Reichweiten-Grenze für BEV von 150 auf 300 km geändert + 400 km bei größerer Batterie/höherem Preissegment</t>
+  </si>
+  <si>
+    <t>Toolversion Stand ergänzen und ifeu-Logo dafür etwas nach oben rücken + Fußzeile nach unten verlängern (siehe PPT in Mail)</t>
+  </si>
+  <si>
+    <t>Gering</t>
+  </si>
+  <si>
+    <t>Zelle B11</t>
+  </si>
+  <si>
+    <t>Reichweiten-Grenze für BEV bei größerer Batterie/höherem Preissegment von 300 auf 400 km geändert</t>
+  </si>
+  <si>
     <t>Hoch</t>
-  </si>
-  <si>
-    <t>Zellen B5-8</t>
-  </si>
-  <si>
-    <t>Reichweiten-Grenze für BEV von 150 auf 300 km geändert + 400 km bei größerer Batterie/höherem Preissegment</t>
-  </si>
-  <si>
-    <t>Toolversion Stand ergänzen und ifeu-Logo dafür etwas nach oben rücken + Fußzeile nach unten verlängern (siehe PPT in Mail)</t>
-  </si>
-  <si>
-    <t>Mittel</t>
   </si>
   <si>
     <t>Abfrage-Empfehlung-Matrix für das DBU-Online-Tool</t>
@@ -3430,7 +3447,30 @@
     <t>E_A8</t>
   </si>
   <si>
-    <t>Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von 300 km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</t>
+    </r>
   </si>
   <si>
     <t>E_A9</t>
@@ -9705,8 +9745,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82AF6CCA-AD25-4D81-BEE9-709B5F3E25B2}" name="Changelog" displayName="Changelog" ref="A1:I117" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2">
-  <autoFilter ref="A1:I117" xr:uid="{AD108A07-7C8F-42B9-AE12-18A3508E5175}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82AF6CCA-AD25-4D81-BEE9-709B5F3E25B2}" name="Changelog" displayName="Changelog" ref="A1:I118" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2">
+  <autoFilter ref="A1:I118" xr:uid="{AD108A07-7C8F-42B9-AE12-18A3508E5175}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{53552D31-9042-42BD-A381-CAE68021C6E6}" name="Änderungsdatum" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{E06889C8-F2D9-4F7E-8D60-4C5289C94E3D}" name="Bearbeitet durch:"/>
@@ -10715,6 +10755,12 @@
   <threadedComment ref="G114" dT="2023-06-28T16:10:02.62" personId="{E1CC788D-457A-48EA-BC7A-C43DB5BFE154}" id="{92BE0025-AE51-4578-BA6B-8322B8FFC01D}" parentId="{CBB4E888-5E8C-437E-B81F-F45FE4BAF6E1}">
     <text>Yeah! Susanne und ich sind happy :-)</text>
   </threadedComment>
+  <threadedComment ref="G117" dT="2024-06-20T10:38:48.59" personId="{E1CC788D-457A-48EA-BC7A-C43DB5BFE154}" id="{30F2D2BD-FBB0-4DD9-B48F-2ADC88252C3F}">
+    <text>Kannst du die Toolversion noch ein ganz bisschen weiter nach unten rücken? So, dass der Abstand zum unteren Seitenrand = Abstand der Logos zum oberen Fußzeilenrand</text>
+  </threadedComment>
+  <threadedComment ref="G117" dT="2024-06-20T11:01:56.81" personId="{2D60394C-DF5F-48A4-A7FB-F2848BF0DE39}" id="{ED8ACAFB-A07F-40A0-8A71-845DF4C3C729}" parentId="{30F2D2BD-FBB0-4DD9-B48F-2ADC88252C3F}">
+    <text>Hab ihn reduziert. Ist nicht exakt, da Text keine klare Unterkante hat</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -10851,7 +10897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35F342AC-F6CA-458C-B812-D66181F53FAD}">
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="51" customWidth="1"/>
@@ -13449,7 +13495,7 @@
         <v>197</v>
       </c>
       <c r="G115" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -13463,13 +13509,13 @@
         <v>131</v>
       </c>
       <c r="D116" t="s">
+        <v>198</v>
+      </c>
+      <c r="E116" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="E116" s="63" t="s">
-        <v>200</v>
-      </c>
       <c r="G116" t="s">
-        <v>198</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -13486,10 +13532,30 @@
         <v>39</v>
       </c>
       <c r="E117" t="s">
+        <v>200</v>
+      </c>
+      <c r="G117" t="s">
         <v>201</v>
       </c>
-      <c r="G117" t="s">
+    </row>
+    <row r="118" spans="1:9" ht="15" customHeight="1">
+      <c r="A118" s="51">
+        <v>45463</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s">
+        <v>131</v>
+      </c>
+      <c r="D118" t="s">
         <v>202</v>
+      </c>
+      <c r="E118" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="G118" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -13553,7 +13619,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -13568,46 +13634,46 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -13615,40 +13681,40 @@
         <v>83</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N4" s="11" t="str">
         <f>E_A1</f>
@@ -13661,40 +13727,40 @@
         <v>83</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L5" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L5" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="M5" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N5" s="2" t="str">
         <f>E_A2</f>
@@ -13707,40 +13773,40 @@
         <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="L6" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="M6" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N6" s="2" t="str">
         <f>E_A3</f>
@@ -13753,40 +13819,40 @@
         <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L7" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="L7" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="M7" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N7" s="2" t="str">
         <f>E_A4</f>
@@ -13799,40 +13865,40 @@
         <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="L8" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="M8" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N8" s="2" t="str">
         <f>E_A5</f>
@@ -13846,40 +13912,40 @@
         <v>83</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L9" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="G9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="I9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="M9" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N9" s="10" t="str">
         <f>E_A6</f>
@@ -13891,40 +13957,40 @@
         <v>83</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N10" s="10" t="str">
         <f>E_A6</f>
@@ -13936,40 +14002,40 @@
         <v>83</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N11" s="2" t="str">
         <f>E_A9</f>
@@ -13981,44 +14047,44 @@
         <v>83</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N12" s="2" t="str">
         <f>E_A8</f>
-        <v>Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von 300 km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</v>
+        <v>Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von 400 km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -14026,40 +14092,40 @@
         <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="J13" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N13" s="2" t="str">
         <f>E_A10</f>
@@ -14071,40 +14137,40 @@
         <v>83</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L14" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N14" s="2" t="str">
         <f>E_A7</f>
@@ -14116,40 +14182,40 @@
         <v>83</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="J15" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N15" s="2" t="str">
         <f>E_A11</f>
@@ -14162,44 +14228,44 @@
         <v>83</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="J16" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L16" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N16" s="2" t="str">
         <f>E_A8</f>
-        <v>Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von 300 km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</v>
+        <v>Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von 400 km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -14207,44 +14273,44 @@
         <v>83</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="J17" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K17" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L17" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N17" s="2" t="str">
         <f>E_A8</f>
-        <v>Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von 300 km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</v>
+        <v>Ein E-Auto (BEV - rein batteriebetrieben) mit großer Reichweite ist ggf. geeignet. In höheren Preissegmenten ist eine Reichweite von 400 km gängig. Es sollte jedoch beachtet werden, dass dem Umweltvorteil eines BEV in der Nutzung die Herstellungsemissionen einer großen Batterie gegenüberstehen. Zudem sind große Batterien vor allem in größeren Fahrzeugen verbaut. Ein kleinerer, möglichst sparsamer Verbrenner kann in diesem Anwendungsfall aus Umweltsicht (und aus Kostensicht ohnehin) also durchaus vorteilhaft sein.</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -14252,40 +14318,40 @@
         <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="J18" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K18" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N18" s="2" t="str">
         <f>E_A11</f>
@@ -14298,40 +14364,40 @@
         <v>85</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C19" s="56" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" s="55" t="s">
+        <v>240</v>
+      </c>
+      <c r="G19" s="55" t="s">
         <v>237</v>
       </c>
-      <c r="D19" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="E19" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="F19" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="G19" s="55" t="s">
-        <v>235</v>
-      </c>
       <c r="H19" s="57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I19" s="57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J19" s="57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K19" s="57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" s="57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M19" s="57" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N19" s="55" t="str">
         <f>E_F1</f>
@@ -14343,40 +14409,40 @@
         <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L20" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N20" s="2" t="str">
         <f>E_F2</f>
@@ -14388,40 +14454,40 @@
         <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I21" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K21" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N21" s="2" t="str">
         <f>E_F3</f>
@@ -14433,40 +14499,40 @@
         <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K22" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N22" s="2" t="str">
         <f>E_F4</f>
@@ -14478,40 +14544,40 @@
         <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N23" s="2" t="str">
         <f>E_F5</f>
@@ -14523,40 +14589,40 @@
         <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="H24" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="M24" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J24" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="K24" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="M24" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="N24" s="2" t="str">
         <f>E_F6</f>
@@ -14568,40 +14634,40 @@
         <v>85</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I25" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K25" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M25" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N25" s="2" t="str">
         <f>E_F7</f>
@@ -14613,40 +14679,40 @@
         <v>85</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I26" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N26" s="2" t="str">
         <f>E_F8</f>
@@ -14658,40 +14724,40 @@
         <v>85</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C27" s="13">
         <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K27" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L27" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M27" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N27" s="2" t="str">
         <f>E_F9</f>
@@ -14703,40 +14769,40 @@
         <v>85</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C28" s="13">
         <v>5</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="I28" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L28" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N28" s="2" t="str">
         <f>E_F10</f>
@@ -14748,40 +14814,40 @@
         <v>85</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L29" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M29" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N29" s="11" t="str">
         <f>E_F11</f>
@@ -14794,40 +14860,40 @@
         <v>85</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L30" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N30" s="11" t="str">
         <f>E_F12</f>
@@ -14840,40 +14906,40 @@
         <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M31" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N31" s="11" t="str">
         <f>E_F13</f>
@@ -14885,40 +14951,40 @@
         <v>85</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I32" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L32" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N32" s="11" t="str">
         <f>E_F14</f>
@@ -14930,40 +14996,40 @@
         <v>85</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="F33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M33" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N33" s="2" t="str">
         <f>E_F15</f>
@@ -14975,40 +15041,40 @@
         <v>85</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I34" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L34" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N34" s="2" t="str">
         <f>E_F16</f>
@@ -15021,40 +15087,40 @@
         <v>85</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L35" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N35" s="2" t="str">
         <f>E_F17</f>
@@ -15067,40 +15133,40 @@
         <v>85</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E36" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H36" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I36" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L36" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M36" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N36" s="2" t="str">
         <f>E_F18</f>
@@ -15112,40 +15178,40 @@
         <v>85</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L37" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N37" s="2" t="str">
         <f>E_F19</f>
@@ -15157,40 +15223,40 @@
         <v>85</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="F38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N38" s="2" t="str">
         <f>E_F20</f>
@@ -15202,40 +15268,40 @@
         <v>85</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L39" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M39" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N39" s="2" t="str">
         <f>E_F21</f>
@@ -15248,40 +15314,40 @@
         <v>85</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L40" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M40" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N40" s="2" t="str">
         <f>E_F22</f>
@@ -15294,40 +15360,40 @@
         <v>85</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J41" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="L41" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="M41" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="L41" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="M41" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="N41" s="2" t="str">
         <f>E_F23</f>
@@ -15340,40 +15406,40 @@
         <v>85</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J42" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="L42" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="K42" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="L42" s="11" t="s">
-        <v>224</v>
-      </c>
       <c r="M42" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N42" s="2" t="str">
         <f>E_F24</f>
@@ -15386,40 +15452,40 @@
         <v>85</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J43" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="L43" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="K43" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="L43" s="11" t="s">
-        <v>224</v>
-      </c>
       <c r="M43" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N43" s="2" t="str">
         <f>E_F25</f>
@@ -15432,40 +15498,40 @@
         <v>85</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J44" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="L44" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="K44" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="L44" s="11" t="s">
-        <v>224</v>
-      </c>
       <c r="M44" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N44" s="2" t="str">
         <f>E_F26</f>
@@ -15478,40 +15544,40 @@
         <v>85</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J45" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="L45" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="M45" s="11" t="s">
         <v>227</v>
-      </c>
-      <c r="L45" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="M45" s="11" t="s">
-        <v>225</v>
       </c>
       <c r="N45" s="2" t="str">
         <f>E_F27</f>
@@ -15524,40 +15590,40 @@
         <v>85</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J46" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="L46" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="K46" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="L46" s="11" t="s">
-        <v>224</v>
-      </c>
       <c r="M46" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N46" s="2" t="str">
         <f>E_F28</f>
@@ -15570,40 +15636,40 @@
         <v>85</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="M47" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="J47" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="L47" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="M47" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="N47" s="2" t="str">
         <f>E_F29</f>
@@ -15616,40 +15682,40 @@
         <v>85</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="M48" s="11" t="s">
         <v>245</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G48" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="I48" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="J48" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="K48" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="L48" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="M48" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="N48" s="2" t="str">
         <f>E_F30</f>
@@ -15662,40 +15728,40 @@
         <v>85</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J49" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="H49" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="I49" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="J49" s="11" t="s">
-        <v>226</v>
-      </c>
       <c r="K49" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L49" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M49" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N49" s="2" t="str">
         <f>E_F31</f>
@@ -15708,40 +15774,40 @@
         <v>85</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J50" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>226</v>
-      </c>
       <c r="K50" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L50" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N50" s="2" t="str">
         <f>E_F32</f>
@@ -15754,40 +15820,40 @@
         <v>85</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E51" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I51" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K51" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="H51" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="I51" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>227</v>
-      </c>
       <c r="L51" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M51" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N51" s="2" t="str">
         <f>E_F33</f>
@@ -15800,40 +15866,40 @@
         <v>85</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L52" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N52" s="2" t="str">
         <f>E_F34</f>
@@ -15846,40 +15912,40 @@
         <v>85</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C53" s="13">
         <v>5</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L53" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M53" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N53" s="2" t="str">
         <f>E_F35</f>
@@ -15892,40 +15958,40 @@
         <v>85</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C54" s="13">
         <v>5</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L54" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N54" s="2" t="str">
         <f>E_F36</f>
@@ -15938,40 +16004,40 @@
         <v>85</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C55" s="13">
         <v>5</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="F55" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L55" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M55" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N55" s="2" t="str">
         <f>E_F37</f>
@@ -15984,40 +16050,40 @@
         <v>85</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C56" s="13">
         <v>5</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L56" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N56" s="2" t="str">
         <f>E_F38</f>
@@ -16030,40 +16096,40 @@
         <v>85</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H57" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I57" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L57" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M57" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N57" s="11" t="str">
         <f>E_F39</f>
@@ -16076,40 +16142,40 @@
         <v>85</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H58" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I58" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L58" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M58" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N58" s="11" t="str">
         <f>E_F40</f>
@@ -16122,40 +16188,40 @@
         <v>85</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E59" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H59" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I59" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L59" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M59" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N59" s="11" t="str">
         <f>E_F41</f>
@@ -16168,40 +16234,40 @@
         <v>85</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E60" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H60" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I60" s="48" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L60" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M60" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N60" s="11" t="str">
         <f>E_F42</f>
@@ -16238,14 +16304,14 @@
     <row r="1" spans="1:6" s="15" customFormat="1" ht="12" customHeight="1"/>
     <row r="2" spans="1:6" s="15" customFormat="1">
       <c r="B2" s="16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="15" customFormat="1"/>
     <row r="4" spans="1:6" s="17" customFormat="1">
       <c r="A4" s="27"/>
       <c r="B4" s="18" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -16255,7 +16321,7 @@
     <row r="5" spans="1:6" s="15" customFormat="1"/>
     <row r="6" spans="1:6" s="16" customFormat="1" ht="14.45">
       <c r="A6" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>83</v>
@@ -16268,7 +16334,7 @@
     <row r="7" spans="1:6" s="15" customFormat="1"/>
     <row r="8" spans="1:6" s="15" customFormat="1" ht="34.15" customHeight="1">
       <c r="B8" s="66" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C8" s="66"/>
       <c r="D8" s="66"/>
@@ -16278,110 +16344,110 @@
     <row r="9" spans="1:6" s="15" customFormat="1"/>
     <row r="10" spans="1:6" s="15" customFormat="1" ht="45" customHeight="1">
       <c r="B10" s="67" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C10" s="67"/>
       <c r="E10" s="20" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="15" customFormat="1">
       <c r="A11" s="15" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B11" s="21">
         <v>200</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:6" s="15" customFormat="1"/>
     <row r="13" spans="1:6" s="15" customFormat="1" ht="14.45">
       <c r="B13" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="15" customFormat="1">
       <c r="A14" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="22" t="s">
         <v>260</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="15" customFormat="1"/>
     <row r="16" spans="1:6" s="15" customFormat="1">
       <c r="B16" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="15" customFormat="1">
       <c r="A17" s="15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="15" customFormat="1"/>
     <row r="19" spans="1:6" s="15" customFormat="1">
       <c r="B19" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:6" s="15" customFormat="1">
       <c r="A20" s="15" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="15" customFormat="1"/>
     <row r="22" spans="1:6" s="15" customFormat="1">
       <c r="B22" s="15" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:6" s="15" customFormat="1">
       <c r="A23" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="15" customFormat="1"/>
     <row r="25" spans="1:6" s="15" customFormat="1">
       <c r="B25" s="15" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:6" s="15" customFormat="1" ht="193.9" customHeight="1">
       <c r="A26" s="34" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B26" s="65" t="str">
         <f>_xlfn.IFS(F_L1=A_JN2, E_A1, AND(F_R1&lt;=A_R1, F_S1=A_S1, F_F1=A_JN1), E_A2, AND(F_R1&lt;=A_R1, F_S1=A_S1, F_F1=A_JN2), E_A3, AND(F_R1&lt;=A_R1, F_S1=A_S2, F_F1=A_JN1), E_A4, AND(F_R1&lt;=A_R1, F_S1=A_S2, F_F1=A_JN2), E_A5, AND(F_R1&lt;=A_R1, F_S1=A_S3), E_A6, AND(F_R1&gt;A_R1, F_S1=A_S1), E_A6, AND(F_R1&gt;A_R1, F_SZ1=A_SV1), E_A9, AND(F_R1&gt;A_R1, F_S1=A_S2, F_SZ1=A_SV2, F_L2=A_JN1), E_A8, AND(F_R1&gt;A_R1, F_SZ1=A_SV2, F_L2=A_JN2), E_A10, AND(F_R1&gt;A_R1, F_S1=A_S2, F_SZ1=A_SV3, F_L2=A_JN1), E_A7, AND(F_R1&gt;A_R1, F_S1=A_S2, F_SZ1=A_SV3, F_L2=A_JN2), E_A11, AND(F_R1&gt;A_R1, F_S1=A_S3, F_SZ1=A_SV2, F_L2=A_JN1), E_A8, AND(F_R1&gt;A_R1, F_S1=A_S3, F_SZ1=A_SV3, F_L2=A_JN1), E_A8, AND(F_R1&gt;A_R1, F_S1=A_S3, F_SZ1=A_SV3, F_L2=A_JN2), E_A11, TRUE, " ")</f>
@@ -16408,7 +16474,7 @@
     <row r="29" spans="1:6" s="15" customFormat="1"/>
     <row r="30" spans="1:6" s="15" customFormat="1" ht="40.9" customHeight="1">
       <c r="B30" s="66" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C30" s="66"/>
       <c r="D30" s="66"/>
@@ -16418,31 +16484,31 @@
     <row r="31" spans="1:6" s="15" customFormat="1"/>
     <row r="32" spans="1:6" s="15" customFormat="1" ht="27.6" customHeight="1">
       <c r="B32" s="67" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C32" s="67"/>
       <c r="E32" s="15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="33" spans="1:6" s="15" customFormat="1">
       <c r="A33" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B33" s="21">
         <v>3</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:6" s="15" customFormat="1">
@@ -16450,10 +16516,10 @@
     </row>
     <row r="35" spans="1:6" s="15" customFormat="1" ht="30" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B35" s="67" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C35" s="67"/>
       <c r="D35" s="67"/>
@@ -16461,13 +16527,13 @@
     </row>
     <row r="36" spans="1:6" s="15" customFormat="1">
       <c r="A36" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E36" s="22"/>
       <c r="F36" s="22"/>
@@ -16475,29 +16541,29 @@
     <row r="37" spans="1:6" s="15" customFormat="1"/>
     <row r="38" spans="1:6" s="15" customFormat="1">
       <c r="B38" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:6" s="15" customFormat="1">
       <c r="A39" s="15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="40" spans="1:6" s="15" customFormat="1"/>
     <row r="41" spans="1:6" s="15" customFormat="1">
       <c r="B41" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="42" spans="1:6" s="15" customFormat="1" ht="102" customHeight="1">
       <c r="A42" s="34" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B42" s="65" t="str">
         <f>_xlfn.IFS(AND(F_P1&lt;6, F_T1=A_T3), E_F1, AND(F_P1&lt;6, OR(F_T1=A_T1, ISBLANK(F_T1)), F_LE1=A_JN1), E_F2, AND(F_P1&gt;=1, F_P1&lt;=2, F_T1=A_T1, F_LE1=A_JN2, F_S1=A_S1), E_F3, AND(F_P1&gt;=1, F_P1&lt;=2, F_T1=A_T1, F_LE1=A_JN2, OR(F_S1=A_S2, F_S1=A_S3)), E_F4, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP1, F_T1=A_T1, F_LE1=A_JN2, F_S1=A_S1), E_F5, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP1, F_T1=A_T1, F_LE1=A_JN2, OR(F_S1=A_S2, F_S1=A_S3)), E_F6, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP2, F_T1=A_T1, F_LE1=A_JN2), E_F7, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP3, F_T1=A_T1, F_LE1=A_JN2), E_F8, AND(F_P1=5, F_SP1=A_SP1, F_T1=A_T1, F_LE1=A_JN2), E_F9, AND(F_P1=5, OR(F_SP1=A_SP2, F_SP1=A_SP3), F_T1=A_T1, F_LE1=A_JN2), E_F10, AND(F_P1&gt;=6, F_P1&lt;=7, F_SP1=A_SP1, F_T1=A_T1, F_F1=A_JN1), E_F11, AND(F_P1&gt;=6, F_P1&lt;=7, F_SP1=A_SP1, F_T1=A_T1, F_F1=A_JN2), E_F12, AND(F_P1&gt;=6, F_P1&lt;=7, F_SP1=A_SP1, F_T1=A_T3, F_F1=A_JN1), E_F13, AND(F_P1&gt;=6, F_P1&lt;=7, F_SP1=A_SP1, F_T1=A_T3, F_F1=A_JN2), E_F14, AND(F_P1&gt;=6, F_P1&lt;=7, OR(F_SP1=A_SP2, F_SP1=A_SP3)), E_F15, AND(F_P1&gt;=8, F_P1&lt;=9, F_SP1=A_SP1, F_T1=A_T1, F_F1=A_JN1), E_F16, AND(F_P1&gt;=8, F_P1&lt;=9, F_SP1=A_SP1, F_T1=A_T1, F_F1=A_JN2), E_F17, AND(F_P1&gt;=8, F_P1&lt;=9, F_SP1=A_SP1, F_T1=A_T3, F_F1=A_JN1), E_F18, AND(F_P1&gt;=8, F_P1&lt;=9, F_SP1=A_SP1, F_T1=A_T3, F_F1=A_JN2), E_F19, AND(F_P1&gt;=8, F_P1&lt;=9, OR(F_SP1=A_SP2, F_SP1=A_SP3)), E_F20, AND(F_P1&lt;6, F_T1=A_T2, F_LE1=A_JN1, F_F1=A_JN1), E_F21, AND(F_P1&lt;6, F_T1=A_T2, F_LE1=A_JN1, F_F1=A_JN2), E_F22, AND(F_P1&gt;=1, F_P1&lt;=2, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1, F_S1=A_S1), E_F23, AND(F_P1&gt;=1, F_P1&lt;=2, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2, F_S1=A_S1), E_F24, AND(F_P1&gt;=1, F_P1&lt;=2, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1, OR(F_S1=A_S2, F_S1=A_S3)), E_F25, AND(F_P1&gt;=1, F_P1&lt;=2, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2, OR(F_S1=A_S2, F_S1=A_S3)), E_F26, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP1, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1, F_S1=A_S1), E_F27, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP1, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2, F_S1=A_S1), E_F28, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP1, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1, OR(F_S1=A_S2, F_S1=A_S3)), E_F29, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP1, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2, OR(F_S1=A_S2, F_S1=A_S3)), E_F30, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP2, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1), E_F31, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP2, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2), E_F32, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP3, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1), E_F33, AND(F_P1&gt;=3, F_P1&lt;=4, F_SP1=A_SP3, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2), E_F34, AND(F_P1=5, F_SP1=A_SP1, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1), E_F35, AND(F_P1=5, F_SP1=A_SP1, F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2), E_F36, AND(F_P1=5, OR(F_SP1=A_SP2, F_SP1=A_SP3), F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN1), E_F37, AND(F_P1=5, OR(F_SP1=A_SP2, F_SP1=A_SP3), F_T1=A_T2, F_LE1=A_JN2, F_F1=A_JN2), E_F38, AND(F_P1&gt;=6, F_P1&lt;=7, F_SP1=A_SP1, F_T1=A_T2, F_F1=A_JN1), E_F39, AND(F_P1&gt;=6, F_P1&lt;=7, F_SP1=A_SP1, F_T1=A_T2, F_F1=A_JN2), E_F40, AND(F_P1&gt;=8, F_P1&lt;=9, F_SP1=A_SP1, F_T1=A_T2, F_F1=A_JN1), E_F41, AND(F_P1&gt;=8, F_P1&lt;=9, F_SP1=A_SP1, F_T1=A_T2, F_F1=A_JN2), E_F42, TRUE, " ")</f>
@@ -16793,14 +16859,14 @@
     <row r="1" spans="1:9" s="15" customFormat="1" ht="12" customHeight="1"/>
     <row r="2" spans="1:9" s="15" customFormat="1">
       <c r="B2" s="16" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C2" s="16"/>
     </row>
     <row r="3" spans="1:9" s="15" customFormat="1"/>
     <row r="4" spans="1:9" s="17" customFormat="1">
       <c r="B4" s="18" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="19"/>
@@ -16814,7 +16880,7 @@
     <row r="6" spans="1:9" s="15" customFormat="1">
       <c r="A6" s="24"/>
       <c r="B6" s="28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C6" s="28"/>
       <c r="D6" s="25"/>
@@ -16827,7 +16893,7 @@
     <row r="7" spans="1:9" s="15" customFormat="1"/>
     <row r="8" spans="1:9" s="15" customFormat="1" ht="71.45" customHeight="1">
       <c r="B8" s="66" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C8" s="66"/>
       <c r="D8" s="66"/>
@@ -16840,12 +16906,12 @@
     <row r="9" spans="1:9" s="15" customFormat="1"/>
     <row r="10" spans="1:9" s="15" customFormat="1">
       <c r="B10" s="15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="15" customFormat="1">
       <c r="A11" s="24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B11" s="68">
         <v>12</v>
@@ -16858,12 +16924,12 @@
     <row r="12" spans="1:9" s="15" customFormat="1"/>
     <row r="13" spans="1:9" s="15" customFormat="1">
       <c r="B13" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="15" customFormat="1">
       <c r="A14" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B14" s="68">
         <v>10</v>
@@ -16916,12 +16982,12 @@
     <row r="18" spans="1:9" s="15" customFormat="1"/>
     <row r="19" spans="1:9" s="15" customFormat="1" ht="19.899999999999999" customHeight="1">
       <c r="B19" s="34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="15" customFormat="1" ht="32.450000000000003" customHeight="1">
       <c r="B20" s="69" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C20" s="69"/>
       <c r="D20" s="69"/>
@@ -16934,67 +17000,67 @@
     <row r="21" spans="1:9" s="15" customFormat="1"/>
     <row r="22" spans="1:9" s="15" customFormat="1" ht="13.9" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="15" customFormat="1" ht="6" customHeight="1"/>
     <row r="24" spans="1:9" s="15" customFormat="1" ht="13.9" customHeight="1">
       <c r="A24" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="15" customFormat="1" ht="6" customHeight="1"/>
     <row r="26" spans="1:9" s="15" customFormat="1" ht="13.9" customHeight="1">
       <c r="A26" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="15" customFormat="1" ht="6" customHeight="1"/>
     <row r="28" spans="1:9" s="15" customFormat="1" ht="13.9" customHeight="1">
       <c r="A28" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="15" customFormat="1" ht="6" customHeight="1"/>
     <row r="30" spans="1:9" s="15" customFormat="1" ht="13.9" customHeight="1">
       <c r="A30" s="15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="15" customFormat="1"/>
     <row r="32" spans="1:9" s="15" customFormat="1">
       <c r="B32" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" s="15" customFormat="1"/>
@@ -17021,13 +17087,13 @@
     <row r="54" spans="1:9" s="15" customFormat="1"/>
     <row r="55" spans="1:9" s="15" customFormat="1" ht="19.149999999999999" customHeight="1">
       <c r="B55" s="32" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C55" s="33"/>
     </row>
     <row r="56" spans="1:9" s="15" customFormat="1" ht="28.15" customHeight="1">
       <c r="B56" s="67" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C56" s="67"/>
       <c r="D56" s="67"/>
@@ -17039,7 +17105,7 @@
     </row>
     <row r="57" spans="1:9" s="15" customFormat="1">
       <c r="A57" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B57" s="68">
         <v>10</v>
@@ -17066,7 +17132,7 @@
     <row r="60" spans="1:9" s="15" customFormat="1"/>
     <row r="61" spans="1:9" s="15" customFormat="1" ht="48.6" customHeight="1">
       <c r="B61" s="67" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C61" s="67"/>
       <c r="D61" s="67"/>
@@ -17174,18 +17240,18 @@
   <sheetData>
     <row r="2" spans="2:9">
       <c r="B2" s="35" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="14.45">
       <c r="B5" s="37" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="2:9">
@@ -17217,21 +17283,21 @@
     </row>
     <row r="10" spans="2:9">
       <c r="B10" s="36" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E10" s="36" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" s="24" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C11" s="35" t="str">
         <f>Fragen_Prototyp_Flotte!$B$30</f>
@@ -17247,7 +17313,7 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="24" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C12" s="35" t="str">
         <f>Fragen_Prototyp_Flotte!$B$28</f>
@@ -17263,7 +17329,7 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="24" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C13" s="35" t="str">
         <f>Fragen_Prototyp_Flotte!$B$26</f>
@@ -17279,7 +17345,7 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="24" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C14" s="35" t="str">
         <f>Fragen_Prototyp_Flotte!$B$24</f>
@@ -17295,7 +17361,7 @@
     </row>
     <row r="15" spans="2:9">
       <c r="B15" s="24" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C15" s="35" t="str">
         <f>Fragen_Prototyp_Flotte!$B$22</f>
@@ -17556,20 +17622,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B4" s="58">
         <v>300</v>
@@ -17577,139 +17643,139 @@
     </row>
     <row r="6" spans="1:2">
       <c r="B6" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B16" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B18" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="B20" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="B25" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -17731,465 +17797,468 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C3" s="62" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="60.75">
       <c r="A4" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="76.5">
       <c r="A5" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B5" s="61" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="60.75">
       <c r="A6" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B6" s="61" t="s">
+        <v>351</v>
+      </c>
+      <c r="C6" s="62" t="s">
         <v>349</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="91.5">
       <c r="A7" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C7" s="62" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="172.5" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C8" s="62" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B10" s="54" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45.75">
       <c r="A11" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B11" s="54" t="s">
-        <v>359</v>
+        <v>360</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="60.75">
       <c r="A14" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C16" s="62" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30.75">
       <c r="A18" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B18" s="54" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30.75">
       <c r="A19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30.75">
       <c r="A20" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B20" s="54" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30.75">
       <c r="A21" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B21" s="54" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30.75">
       <c r="A22" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30.75">
       <c r="A23" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B23" s="54" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="30.75">
       <c r="A24" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B24" s="54" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30.75">
       <c r="A25" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B25" s="54" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B26" s="30" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="60.75">
       <c r="A27" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B27" s="54" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="60.75">
       <c r="A28" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B28" s="54" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="45.75">
       <c r="A29" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="45.75">
       <c r="A30" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B30" s="54" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60.75">
       <c r="A32" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B32" s="54" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="66" customHeight="1">
       <c r="A33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B33" s="54" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="45.75">
       <c r="A34" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="45.75">
       <c r="A35" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="76.5">
       <c r="A37" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B37" s="54" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="60.75">
       <c r="A38" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B38" s="54" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="76.5">
       <c r="A39" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B39" s="54" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="60.75">
       <c r="A40" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B40" s="54" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="76.5">
       <c r="A41" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B41" s="54" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="60.75">
       <c r="A42" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B42" s="54" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="76.5">
       <c r="A43" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B43" s="54" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="60.75">
       <c r="A44" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B44" s="54" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="76.5">
       <c r="A45" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B45" s="54" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60.75">
       <c r="A46" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B46" s="54" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="76.5">
       <c r="A47" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B47" s="54" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="60.75">
       <c r="A48" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B48" s="54" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="76.5">
       <c r="A49" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B49" s="54" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="60.75">
       <c r="A50" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B50" s="54" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="76.5">
       <c r="A51" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B51" s="54" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="60.75">
       <c r="A52" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B52" s="54" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="60.75">
       <c r="A53" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="45.75">
       <c r="A54" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="60.75">
       <c r="A55" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="60.75">
       <c r="A56" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B56" s="54" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="60.75">
       <c r="A57" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B57" s="54" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="60.75">
       <c r="A58" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B58" s="54" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -18210,105 +18279,105 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B3" s="43" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" s="43" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="28.9">
       <c r="A8" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="28.9">
       <c r="A9" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="28.9">
       <c r="A10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" s="43" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="28.9">
       <c r="A14" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="43.15">
       <c r="A16" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="43.15">
       <c r="A17" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -18318,12 +18387,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101009B43F9A2BF99C145A97E1F24240CACC5" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="69fdfa13dcb573d0d17606fa18021a49">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0b6e3095-4fd5-4f76-ae54-62b873214d55" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f1f6d0d576ec092377ed985f5102cf0c" ns2:_="">
     <xsd:import namespace="0b6e3095-4fd5-4f76-ae54-62b873214d55"/>
@@ -18467,23 +18545,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C88A46BD-075C-4460-ABD3-5E8F1283600A}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4945DDDB-1595-4E42-8B3F-72E43B1AB0DA}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C237155-F302-499A-A6E1-BDAF97A0B05D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C88A46BD-075C-4460-ABD3-5E8F1283600A}"/>
 </file>